--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075211</v>
+        <v>120074893</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478402</v>
+        <v>478394</v>
       </c>
       <c r="R2" t="n">
         <v>6827537</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075114</v>
+        <v>120074900</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478430</v>
+        <v>478411</v>
       </c>
       <c r="R3" t="n">
-        <v>6827596</v>
+        <v>6827584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074902</v>
+        <v>120075111</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478397</v>
+        <v>478498</v>
       </c>
       <c r="R4" t="n">
-        <v>6827585</v>
+        <v>6827561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075034</v>
+        <v>120075101</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478379</v>
+        <v>478411</v>
       </c>
       <c r="R5" t="n">
-        <v>6827599</v>
+        <v>6827532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075116</v>
+        <v>120075109</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478396</v>
+        <v>478505</v>
       </c>
       <c r="R6" t="n">
-        <v>6827595</v>
+        <v>6827549</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075111</v>
+        <v>120075006</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478498</v>
+        <v>478379</v>
       </c>
       <c r="R7" t="n">
-        <v>6827561</v>
+        <v>6827599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120074893</v>
+        <v>120075211</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478394</v>
+        <v>478402</v>
       </c>
       <c r="R8" t="n">
         <v>6827537</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075033</v>
+        <v>120075210</v>
       </c>
       <c r="B9" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478398</v>
+        <v>478399</v>
       </c>
       <c r="R9" t="n">
-        <v>6827585</v>
+        <v>6827538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120074990</v>
+        <v>120075030</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,39 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478450</v>
+        <v>478428</v>
       </c>
       <c r="R10" t="n">
-        <v>6827577</v>
+        <v>6827530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075115</v>
+        <v>120075033</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478417</v>
+        <v>478398</v>
       </c>
       <c r="R11" t="n">
-        <v>6827606</v>
+        <v>6827585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075199</v>
+        <v>120074903</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478451</v>
+        <v>478380</v>
       </c>
       <c r="R12" t="n">
-        <v>6827576</v>
+        <v>6827599</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075113</v>
+        <v>120074953</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478441</v>
+        <v>478428</v>
       </c>
       <c r="R13" t="n">
-        <v>6827579</v>
+        <v>6827530</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075209</v>
+        <v>120074894</v>
       </c>
       <c r="B14" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478401</v>
+        <v>478491</v>
       </c>
       <c r="R14" t="n">
-        <v>6827551</v>
+        <v>6827539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075109</v>
+        <v>120075056</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478505</v>
+        <v>478506</v>
       </c>
       <c r="R15" t="n">
-        <v>6827549</v>
+        <v>6827552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075210</v>
+        <v>120074896</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478399</v>
+        <v>478480</v>
       </c>
       <c r="R16" t="n">
-        <v>6827538</v>
+        <v>6827565</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075030</v>
+        <v>120075115</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478428</v>
+        <v>478417</v>
       </c>
       <c r="R17" t="n">
-        <v>6827530</v>
+        <v>6827606</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075101</v>
+        <v>120075105</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478411</v>
+        <v>478466</v>
       </c>
       <c r="R18" t="n">
-        <v>6827532</v>
+        <v>6827519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120074894</v>
+        <v>120075034</v>
       </c>
       <c r="B19" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478491</v>
+        <v>478379</v>
       </c>
       <c r="R19" t="n">
-        <v>6827539</v>
+        <v>6827599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075031</v>
+        <v>120075113</v>
       </c>
       <c r="B20" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478492</v>
+        <v>478441</v>
       </c>
       <c r="R20" t="n">
-        <v>6827538</v>
+        <v>6827579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075102</v>
+        <v>120074898</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478430</v>
+        <v>478443</v>
       </c>
       <c r="R21" t="n">
-        <v>6827531</v>
+        <v>6827578</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120074896</v>
+        <v>120075209</v>
       </c>
       <c r="B22" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478480</v>
+        <v>478401</v>
       </c>
       <c r="R22" t="n">
-        <v>6827565</v>
+        <v>6827551</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075056</v>
+        <v>120074958</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478506</v>
+        <v>478491</v>
       </c>
       <c r="R23" t="n">
-        <v>6827552</v>
+        <v>6827538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074953</v>
+        <v>120074990</v>
       </c>
       <c r="B24" t="n">
-        <v>79115</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,34 +2935,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478428</v>
+        <v>478450</v>
       </c>
       <c r="R24" t="n">
-        <v>6827530</v>
+        <v>6827577</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075112</v>
+        <v>120075102</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478453</v>
+        <v>478430</v>
       </c>
       <c r="R25" t="n">
-        <v>6827573</v>
+        <v>6827531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075100</v>
+        <v>120075112</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478398</v>
+        <v>478453</v>
       </c>
       <c r="R26" t="n">
-        <v>6827537</v>
+        <v>6827573</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074898</v>
+        <v>120074902</v>
       </c>
       <c r="B27" t="n">
         <v>79144</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478443</v>
+        <v>478397</v>
       </c>
       <c r="R27" t="n">
-        <v>6827578</v>
+        <v>6827585</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074903</v>
+        <v>120074918</v>
       </c>
       <c r="B28" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478380</v>
+        <v>478466</v>
       </c>
       <c r="R28" t="n">
-        <v>6827599</v>
+        <v>6827519</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074900</v>
+        <v>120075199</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478411</v>
+        <v>478451</v>
       </c>
       <c r="R29" t="n">
-        <v>6827584</v>
+        <v>6827576</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075105</v>
+        <v>120075100</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478466</v>
+        <v>478398</v>
       </c>
       <c r="R30" t="n">
-        <v>6827519</v>
+        <v>6827537</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074958</v>
+        <v>120075116</v>
       </c>
       <c r="B31" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478491</v>
+        <v>478396</v>
       </c>
       <c r="R31" t="n">
-        <v>6827538</v>
+        <v>6827595</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075006</v>
+        <v>120075114</v>
       </c>
       <c r="B32" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478379</v>
+        <v>478430</v>
       </c>
       <c r="R32" t="n">
-        <v>6827599</v>
+        <v>6827596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074918</v>
+        <v>120075031</v>
       </c>
       <c r="B33" t="n">
-        <v>78560</v>
+        <v>78262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478466</v>
+        <v>478492</v>
       </c>
       <c r="R33" t="n">
-        <v>6827519</v>
+        <v>6827538</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074893</v>
+        <v>120075111</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478394</v>
+        <v>478498</v>
       </c>
       <c r="R2" t="n">
-        <v>6827537</v>
+        <v>6827561</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074900</v>
+        <v>120074893</v>
       </c>
       <c r="B3" t="n">
         <v>79144</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478411</v>
+        <v>478394</v>
       </c>
       <c r="R3" t="n">
-        <v>6827584</v>
+        <v>6827537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075111</v>
+        <v>120074900</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478498</v>
+        <v>478411</v>
       </c>
       <c r="R4" t="n">
-        <v>6827561</v>
+        <v>6827584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075056</v>
+        <v>120074896</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>79144</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478506</v>
+        <v>478480</v>
       </c>
       <c r="R15" t="n">
-        <v>6827552</v>
+        <v>6827565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120074896</v>
+        <v>120075056</v>
       </c>
       <c r="B16" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478480</v>
+        <v>478506</v>
       </c>
       <c r="R16" t="n">
-        <v>6827565</v>
+        <v>6827552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075113</v>
+        <v>120075209</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478441</v>
+        <v>478401</v>
       </c>
       <c r="R20" t="n">
-        <v>6827579</v>
+        <v>6827551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074898</v>
+        <v>120075113</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478443</v>
+        <v>478441</v>
       </c>
       <c r="R21" t="n">
-        <v>6827578</v>
+        <v>6827579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075209</v>
+        <v>120074898</v>
       </c>
       <c r="B22" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478401</v>
+        <v>478443</v>
       </c>
       <c r="R22" t="n">
-        <v>6827551</v>
+        <v>6827578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074958</v>
+        <v>120074990</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,34 +2833,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478491</v>
+        <v>478450</v>
       </c>
       <c r="R23" t="n">
-        <v>6827538</v>
+        <v>6827577</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2898,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074990</v>
+        <v>120074958</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,39 +2945,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478450</v>
+        <v>478491</v>
       </c>
       <c r="R24" t="n">
-        <v>6827577</v>
+        <v>6827538</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074902</v>
+        <v>120074918</v>
       </c>
       <c r="B27" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478397</v>
+        <v>478466</v>
       </c>
       <c r="R27" t="n">
-        <v>6827585</v>
+        <v>6827519</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074918</v>
+        <v>120074902</v>
       </c>
       <c r="B28" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478466</v>
+        <v>478397</v>
       </c>
       <c r="R28" t="n">
-        <v>6827519</v>
+        <v>6827585</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075199</v>
+        <v>120075100</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3451,25 +3451,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478451</v>
+        <v>478398</v>
       </c>
       <c r="R29" t="n">
-        <v>6827576</v>
+        <v>6827537</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075100</v>
+        <v>120075199</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478398</v>
+        <v>478451</v>
       </c>
       <c r="R30" t="n">
-        <v>6827537</v>
+        <v>6827576</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075111</v>
+        <v>120074990</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478498</v>
+        <v>478450</v>
       </c>
       <c r="R2" t="n">
-        <v>6827561</v>
+        <v>6827577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074893</v>
+        <v>120074903</v>
       </c>
       <c r="B3" t="n">
         <v>79144</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478394</v>
+        <v>478380</v>
       </c>
       <c r="R3" t="n">
-        <v>6827537</v>
+        <v>6827599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074900</v>
+        <v>120074893</v>
       </c>
       <c r="B4" t="n">
         <v>79144</v>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478411</v>
+        <v>478394</v>
       </c>
       <c r="R4" t="n">
-        <v>6827584</v>
+        <v>6827537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075101</v>
+        <v>120075209</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478411</v>
+        <v>478401</v>
       </c>
       <c r="R5" t="n">
-        <v>6827532</v>
+        <v>6827551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075109</v>
+        <v>120075100</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478505</v>
+        <v>478398</v>
       </c>
       <c r="R6" t="n">
-        <v>6827549</v>
+        <v>6827537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075006</v>
+        <v>120074902</v>
       </c>
       <c r="B7" t="n">
-        <v>78263</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478379</v>
+        <v>478397</v>
       </c>
       <c r="R7" t="n">
-        <v>6827599</v>
+        <v>6827585</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075211</v>
+        <v>120075056</v>
       </c>
       <c r="B8" t="n">
-        <v>78171</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478402</v>
+        <v>478506</v>
       </c>
       <c r="R8" t="n">
-        <v>6827537</v>
+        <v>6827552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075210</v>
+        <v>120074898</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478399</v>
+        <v>478443</v>
       </c>
       <c r="R9" t="n">
-        <v>6827538</v>
+        <v>6827578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075030</v>
+        <v>120075115</v>
       </c>
       <c r="B10" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478428</v>
+        <v>478417</v>
       </c>
       <c r="R10" t="n">
-        <v>6827530</v>
+        <v>6827606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075033</v>
+        <v>120075211</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478398</v>
+        <v>478402</v>
       </c>
       <c r="R11" t="n">
-        <v>6827585</v>
+        <v>6827537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120074903</v>
+        <v>120075199</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478380</v>
+        <v>478451</v>
       </c>
       <c r="R12" t="n">
-        <v>6827599</v>
+        <v>6827576</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120074953</v>
+        <v>120075034</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478428</v>
+        <v>478379</v>
       </c>
       <c r="R13" t="n">
-        <v>6827530</v>
+        <v>6827599</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074894</v>
+        <v>120074958</v>
       </c>
       <c r="B14" t="n">
-        <v>79144</v>
+        <v>57463</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,7 +1952,7 @@
         <v>478491</v>
       </c>
       <c r="R14" t="n">
-        <v>6827539</v>
+        <v>6827538</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074896</v>
+        <v>120074918</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478480</v>
+        <v>478466</v>
       </c>
       <c r="R15" t="n">
-        <v>6827565</v>
+        <v>6827519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075056</v>
+        <v>120074953</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>79115</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478506</v>
+        <v>478428</v>
       </c>
       <c r="R16" t="n">
-        <v>6827552</v>
+        <v>6827530</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2215,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075115</v>
+        <v>120075113</v>
       </c>
       <c r="B17" t="n">
         <v>78526</v>
@@ -2245,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478417</v>
+        <v>478441</v>
       </c>
       <c r="R17" t="n">
-        <v>6827606</v>
+        <v>6827579</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075105</v>
+        <v>120075101</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2347,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478466</v>
+        <v>478411</v>
       </c>
       <c r="R18" t="n">
-        <v>6827519</v>
+        <v>6827532</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075034</v>
+        <v>120075112</v>
       </c>
       <c r="B19" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478379</v>
+        <v>478453</v>
       </c>
       <c r="R19" t="n">
-        <v>6827599</v>
+        <v>6827573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075209</v>
+        <v>120075114</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478401</v>
+        <v>478430</v>
       </c>
       <c r="R20" t="n">
-        <v>6827551</v>
+        <v>6827596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075113</v>
+        <v>120074896</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478441</v>
+        <v>478480</v>
       </c>
       <c r="R21" t="n">
-        <v>6827579</v>
+        <v>6827565</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120074898</v>
+        <v>120075006</v>
       </c>
       <c r="B22" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478443</v>
+        <v>478379</v>
       </c>
       <c r="R22" t="n">
-        <v>6827578</v>
+        <v>6827599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074990</v>
+        <v>120075105</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,39 +2843,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478450</v>
+        <v>478466</v>
       </c>
       <c r="R23" t="n">
-        <v>6827577</v>
+        <v>6827519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2898,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074958</v>
+        <v>120075030</v>
       </c>
       <c r="B24" t="n">
-        <v>57463</v>
+        <v>78262</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478491</v>
+        <v>478428</v>
       </c>
       <c r="R24" t="n">
-        <v>6827538</v>
+        <v>6827530</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075102</v>
+        <v>120074900</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478430</v>
+        <v>478411</v>
       </c>
       <c r="R25" t="n">
-        <v>6827531</v>
+        <v>6827584</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075112</v>
+        <v>120075109</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478453</v>
+        <v>478505</v>
       </c>
       <c r="R26" t="n">
-        <v>6827573</v>
+        <v>6827549</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074918</v>
+        <v>120074894</v>
       </c>
       <c r="B27" t="n">
-        <v>78560</v>
+        <v>79144</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478466</v>
+        <v>478491</v>
       </c>
       <c r="R27" t="n">
-        <v>6827519</v>
+        <v>6827539</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074902</v>
+        <v>120075033</v>
       </c>
       <c r="B28" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478397</v>
+        <v>478398</v>
       </c>
       <c r="R28" t="n">
         <v>6827585</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075100</v>
+        <v>120075210</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478398</v>
+        <v>478399</v>
       </c>
       <c r="R29" t="n">
-        <v>6827537</v>
+        <v>6827538</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075199</v>
+        <v>120075116</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478451</v>
+        <v>478396</v>
       </c>
       <c r="R30" t="n">
-        <v>6827576</v>
+        <v>6827595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075116</v>
+        <v>120075111</v>
       </c>
       <c r="B31" t="n">
         <v>78526</v>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478396</v>
+        <v>478498</v>
       </c>
       <c r="R31" t="n">
-        <v>6827595</v>
+        <v>6827561</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075114</v>
+        <v>120075031</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478430</v>
+        <v>478492</v>
       </c>
       <c r="R32" t="n">
-        <v>6827596</v>
+        <v>6827538</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075031</v>
+        <v>120075102</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478492</v>
+        <v>478430</v>
       </c>
       <c r="R33" t="n">
-        <v>6827538</v>
+        <v>6827531</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075100</v>
+        <v>120075056</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478398</v>
+        <v>478506</v>
       </c>
       <c r="R6" t="n">
-        <v>6827537</v>
+        <v>6827552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075056</v>
+        <v>120075100</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478506</v>
+        <v>478398</v>
       </c>
       <c r="R8" t="n">
-        <v>6827552</v>
+        <v>6827537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120074898</v>
+        <v>120075115</v>
       </c>
       <c r="B9" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478443</v>
+        <v>478417</v>
       </c>
       <c r="R9" t="n">
-        <v>6827578</v>
+        <v>6827606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075115</v>
+        <v>120074898</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478417</v>
+        <v>478443</v>
       </c>
       <c r="R10" t="n">
-        <v>6827606</v>
+        <v>6827578</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075112</v>
+        <v>120074896</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478453</v>
+        <v>478480</v>
       </c>
       <c r="R19" t="n">
-        <v>6827573</v>
+        <v>6827565</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075114</v>
+        <v>120075112</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478430</v>
+        <v>478453</v>
       </c>
       <c r="R20" t="n">
-        <v>6827596</v>
+        <v>6827573</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074896</v>
+        <v>120075114</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478480</v>
+        <v>478430</v>
       </c>
       <c r="R21" t="n">
-        <v>6827565</v>
+        <v>6827596</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120074990</v>
+        <v>120075113</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478450</v>
+        <v>478441</v>
       </c>
       <c r="R2" t="n">
-        <v>6827577</v>
+        <v>6827579</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074903</v>
+        <v>120075210</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478380</v>
+        <v>478399</v>
       </c>
       <c r="R3" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074893</v>
+        <v>120074903</v>
       </c>
       <c r="B4" t="n">
         <v>79144</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478394</v>
+        <v>478380</v>
       </c>
       <c r="R4" t="n">
-        <v>6827537</v>
+        <v>6827599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075209</v>
+        <v>120075033</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478401</v>
+        <v>478398</v>
       </c>
       <c r="R5" t="n">
-        <v>6827551</v>
+        <v>6827585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075056</v>
+        <v>120075006</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478506</v>
+        <v>478379</v>
       </c>
       <c r="R6" t="n">
-        <v>6827552</v>
+        <v>6827599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074902</v>
+        <v>120075199</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478397</v>
+        <v>478451</v>
       </c>
       <c r="R7" t="n">
-        <v>6827585</v>
+        <v>6827576</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075100</v>
+        <v>120075102</v>
       </c>
       <c r="B8" t="n">
         <v>78526</v>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478398</v>
+        <v>478430</v>
       </c>
       <c r="R8" t="n">
-        <v>6827537</v>
+        <v>6827531</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075115</v>
+        <v>120075111</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478417</v>
+        <v>478498</v>
       </c>
       <c r="R9" t="n">
-        <v>6827606</v>
+        <v>6827561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120074898</v>
+        <v>120074918</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478443</v>
+        <v>478466</v>
       </c>
       <c r="R10" t="n">
-        <v>6827578</v>
+        <v>6827519</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075211</v>
+        <v>120075031</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478402</v>
+        <v>478492</v>
       </c>
       <c r="R11" t="n">
-        <v>6827537</v>
+        <v>6827538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075199</v>
+        <v>120075116</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478451</v>
+        <v>478396</v>
       </c>
       <c r="R12" t="n">
-        <v>6827576</v>
+        <v>6827595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075034</v>
+        <v>120074900</v>
       </c>
       <c r="B13" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478379</v>
+        <v>478411</v>
       </c>
       <c r="R13" t="n">
-        <v>6827599</v>
+        <v>6827584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074958</v>
+        <v>120074902</v>
       </c>
       <c r="B14" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478491</v>
+        <v>478397</v>
       </c>
       <c r="R14" t="n">
-        <v>6827538</v>
+        <v>6827585</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074918</v>
+        <v>120074990</v>
       </c>
       <c r="B15" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2017,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478466</v>
+        <v>478450</v>
       </c>
       <c r="R15" t="n">
-        <v>6827519</v>
+        <v>6827577</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120074953</v>
+        <v>120075034</v>
       </c>
       <c r="B16" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478428</v>
+        <v>478379</v>
       </c>
       <c r="R16" t="n">
-        <v>6827530</v>
+        <v>6827599</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075113</v>
+        <v>120075211</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478441</v>
+        <v>478402</v>
       </c>
       <c r="R17" t="n">
-        <v>6827579</v>
+        <v>6827537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075101</v>
+        <v>120075209</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478411</v>
+        <v>478401</v>
       </c>
       <c r="R18" t="n">
-        <v>6827532</v>
+        <v>6827551</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120074896</v>
+        <v>120074894</v>
       </c>
       <c r="B19" t="n">
         <v>79144</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478480</v>
+        <v>478491</v>
       </c>
       <c r="R19" t="n">
-        <v>6827565</v>
+        <v>6827539</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075112</v>
+        <v>120075100</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478453</v>
+        <v>478398</v>
       </c>
       <c r="R20" t="n">
-        <v>6827573</v>
+        <v>6827537</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075114</v>
+        <v>120074898</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478430</v>
+        <v>478443</v>
       </c>
       <c r="R21" t="n">
-        <v>6827596</v>
+        <v>6827578</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075006</v>
+        <v>120075109</v>
       </c>
       <c r="B22" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478379</v>
+        <v>478505</v>
       </c>
       <c r="R22" t="n">
-        <v>6827599</v>
+        <v>6827549</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075105</v>
+        <v>120075114</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478466</v>
+        <v>478430</v>
       </c>
       <c r="R23" t="n">
-        <v>6827519</v>
+        <v>6827596</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075030</v>
+        <v>120075105</v>
       </c>
       <c r="B24" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478428</v>
+        <v>478466</v>
       </c>
       <c r="R24" t="n">
-        <v>6827530</v>
+        <v>6827519</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120074900</v>
+        <v>120075115</v>
       </c>
       <c r="B25" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478411</v>
+        <v>478417</v>
       </c>
       <c r="R25" t="n">
-        <v>6827584</v>
+        <v>6827606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075109</v>
+        <v>120074893</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478505</v>
+        <v>478394</v>
       </c>
       <c r="R26" t="n">
-        <v>6827549</v>
+        <v>6827537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074894</v>
+        <v>120075056</v>
       </c>
       <c r="B27" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478491</v>
+        <v>478506</v>
       </c>
       <c r="R27" t="n">
-        <v>6827539</v>
+        <v>6827552</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075033</v>
+        <v>120075101</v>
       </c>
       <c r="B28" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478398</v>
+        <v>478411</v>
       </c>
       <c r="R28" t="n">
-        <v>6827585</v>
+        <v>6827532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075210</v>
+        <v>120075030</v>
       </c>
       <c r="B29" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478399</v>
+        <v>478428</v>
       </c>
       <c r="R29" t="n">
-        <v>6827538</v>
+        <v>6827530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075116</v>
+        <v>120074896</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478396</v>
+        <v>478480</v>
       </c>
       <c r="R30" t="n">
-        <v>6827595</v>
+        <v>6827565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075111</v>
+        <v>120074953</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79115</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478498</v>
+        <v>478428</v>
       </c>
       <c r="R31" t="n">
-        <v>6827561</v>
+        <v>6827530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075031</v>
+        <v>120075112</v>
       </c>
       <c r="B32" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478492</v>
+        <v>478453</v>
       </c>
       <c r="R32" t="n">
-        <v>6827538</v>
+        <v>6827573</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075102</v>
+        <v>120074958</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478430</v>
+        <v>478491</v>
       </c>
       <c r="R33" t="n">
-        <v>6827531</v>
+        <v>6827538</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075210</v>
+        <v>120074903</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478399</v>
+        <v>478380</v>
       </c>
       <c r="R3" t="n">
-        <v>6827538</v>
+        <v>6827599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074903</v>
+        <v>120075033</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478380</v>
+        <v>478398</v>
       </c>
       <c r="R4" t="n">
-        <v>6827599</v>
+        <v>6827585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075033</v>
+        <v>120075006</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478398</v>
+        <v>478379</v>
       </c>
       <c r="R5" t="n">
-        <v>6827585</v>
+        <v>6827599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075006</v>
+        <v>120075210</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478379</v>
+        <v>478399</v>
       </c>
       <c r="R6" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075031</v>
+        <v>120075116</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478492</v>
+        <v>478396</v>
       </c>
       <c r="R11" t="n">
-        <v>6827538</v>
+        <v>6827595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075116</v>
+        <v>120075031</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478396</v>
+        <v>478492</v>
       </c>
       <c r="R12" t="n">
-        <v>6827595</v>
+        <v>6827538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075056</v>
+        <v>120075101</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478506</v>
+        <v>478411</v>
       </c>
       <c r="R27" t="n">
-        <v>6827552</v>
+        <v>6827532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075101</v>
+        <v>120075030</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478411</v>
+        <v>478428</v>
       </c>
       <c r="R28" t="n">
-        <v>6827532</v>
+        <v>6827530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075030</v>
+        <v>120074896</v>
       </c>
       <c r="B29" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478428</v>
+        <v>478480</v>
       </c>
       <c r="R29" t="n">
-        <v>6827530</v>
+        <v>6827565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074896</v>
+        <v>120075056</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478480</v>
+        <v>478506</v>
       </c>
       <c r="R30" t="n">
-        <v>6827565</v>
+        <v>6827552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074903</v>
+        <v>120075210</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478380</v>
+        <v>478399</v>
       </c>
       <c r="R3" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075033</v>
+        <v>120074903</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478398</v>
+        <v>478380</v>
       </c>
       <c r="R4" t="n">
-        <v>6827585</v>
+        <v>6827599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075006</v>
+        <v>120075033</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478379</v>
+        <v>478398</v>
       </c>
       <c r="R5" t="n">
-        <v>6827599</v>
+        <v>6827585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075210</v>
+        <v>120075006</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478399</v>
+        <v>478379</v>
       </c>
       <c r="R6" t="n">
-        <v>6827538</v>
+        <v>6827599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075116</v>
+        <v>120075031</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478396</v>
+        <v>478492</v>
       </c>
       <c r="R11" t="n">
-        <v>6827595</v>
+        <v>6827538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075031</v>
+        <v>120075116</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478492</v>
+        <v>478396</v>
       </c>
       <c r="R12" t="n">
-        <v>6827538</v>
+        <v>6827595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075101</v>
+        <v>120075056</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478411</v>
+        <v>478506</v>
       </c>
       <c r="R27" t="n">
-        <v>6827532</v>
+        <v>6827552</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075030</v>
+        <v>120075101</v>
       </c>
       <c r="B28" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478428</v>
+        <v>478411</v>
       </c>
       <c r="R28" t="n">
-        <v>6827530</v>
+        <v>6827532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074896</v>
+        <v>120075030</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478480</v>
+        <v>478428</v>
       </c>
       <c r="R29" t="n">
-        <v>6827565</v>
+        <v>6827530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075056</v>
+        <v>120074896</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>79144</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478506</v>
+        <v>478480</v>
       </c>
       <c r="R30" t="n">
-        <v>6827552</v>
+        <v>6827565</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120074894</v>
+        <v>120075100</v>
       </c>
       <c r="B19" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478491</v>
+        <v>478398</v>
       </c>
       <c r="R19" t="n">
-        <v>6827539</v>
+        <v>6827537</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075100</v>
+        <v>120074894</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478398</v>
+        <v>478491</v>
       </c>
       <c r="R20" t="n">
-        <v>6827537</v>
+        <v>6827539</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075056</v>
+        <v>120075101</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478506</v>
+        <v>478411</v>
       </c>
       <c r="R27" t="n">
-        <v>6827552</v>
+        <v>6827532</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075101</v>
+        <v>120075030</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478411</v>
+        <v>478428</v>
       </c>
       <c r="R28" t="n">
-        <v>6827532</v>
+        <v>6827530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075030</v>
+        <v>120074896</v>
       </c>
       <c r="B29" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478428</v>
+        <v>478480</v>
       </c>
       <c r="R29" t="n">
-        <v>6827530</v>
+        <v>6827565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074896</v>
+        <v>120075056</v>
       </c>
       <c r="B30" t="n">
-        <v>79144</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478480</v>
+        <v>478506</v>
       </c>
       <c r="R30" t="n">
-        <v>6827565</v>
+        <v>6827552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075210</v>
+        <v>120074903</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478399</v>
+        <v>478380</v>
       </c>
       <c r="R3" t="n">
-        <v>6827538</v>
+        <v>6827599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074903</v>
+        <v>120075033</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478380</v>
+        <v>478398</v>
       </c>
       <c r="R4" t="n">
-        <v>6827599</v>
+        <v>6827585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075033</v>
+        <v>120075006</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478398</v>
+        <v>478379</v>
       </c>
       <c r="R5" t="n">
-        <v>6827585</v>
+        <v>6827599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075006</v>
+        <v>120075210</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478379</v>
+        <v>478399</v>
       </c>
       <c r="R6" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075211</v>
+        <v>120075100</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478402</v>
+        <v>478398</v>
       </c>
       <c r="R17" t="n">
         <v>6827537</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075209</v>
+        <v>120075211</v>
       </c>
       <c r="B18" t="n">
         <v>78171</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478401</v>
+        <v>478402</v>
       </c>
       <c r="R18" t="n">
-        <v>6827551</v>
+        <v>6827537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075100</v>
+        <v>120075209</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478398</v>
+        <v>478401</v>
       </c>
       <c r="R19" t="n">
-        <v>6827537</v>
+        <v>6827551</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074903</v>
+        <v>120075210</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478380</v>
+        <v>478399</v>
       </c>
       <c r="R3" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075033</v>
+        <v>120074903</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478398</v>
+        <v>478380</v>
       </c>
       <c r="R4" t="n">
-        <v>6827585</v>
+        <v>6827599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075006</v>
+        <v>120075033</v>
       </c>
       <c r="B5" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478379</v>
+        <v>478398</v>
       </c>
       <c r="R5" t="n">
-        <v>6827599</v>
+        <v>6827585</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075210</v>
+        <v>120075006</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478399</v>
+        <v>478379</v>
       </c>
       <c r="R6" t="n">
-        <v>6827538</v>
+        <v>6827599</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075031</v>
+        <v>120075116</v>
       </c>
       <c r="B11" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478492</v>
+        <v>478396</v>
       </c>
       <c r="R11" t="n">
-        <v>6827538</v>
+        <v>6827595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075116</v>
+        <v>120075031</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478396</v>
+        <v>478492</v>
       </c>
       <c r="R12" t="n">
-        <v>6827595</v>
+        <v>6827538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075113</v>
+        <v>120075211</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478441</v>
+        <v>478402</v>
       </c>
       <c r="R2" t="n">
-        <v>6827579</v>
+        <v>6827537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075210</v>
+        <v>120075006</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>78279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478399</v>
+        <v>478379</v>
       </c>
       <c r="R3" t="n">
-        <v>6827538</v>
+        <v>6827599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074903</v>
+        <v>120075199</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478380</v>
+        <v>478451</v>
       </c>
       <c r="R4" t="n">
-        <v>6827599</v>
+        <v>6827576</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075033</v>
+        <v>120075102</v>
       </c>
       <c r="B5" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478398</v>
+        <v>478430</v>
       </c>
       <c r="R5" t="n">
-        <v>6827585</v>
+        <v>6827531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075006</v>
+        <v>120075114</v>
       </c>
       <c r="B6" t="n">
-        <v>78263</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478379</v>
+        <v>478430</v>
       </c>
       <c r="R6" t="n">
-        <v>6827599</v>
+        <v>6827596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075199</v>
+        <v>120074958</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478451</v>
+        <v>478491</v>
       </c>
       <c r="R7" t="n">
-        <v>6827576</v>
+        <v>6827538</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075102</v>
+        <v>120075112</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478430</v>
+        <v>478453</v>
       </c>
       <c r="R8" t="n">
-        <v>6827531</v>
+        <v>6827573</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075111</v>
+        <v>120074893</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478498</v>
+        <v>478394</v>
       </c>
       <c r="R9" t="n">
-        <v>6827561</v>
+        <v>6827537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120074918</v>
+        <v>120074953</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>79131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478466</v>
+        <v>478428</v>
       </c>
       <c r="R10" t="n">
-        <v>6827519</v>
+        <v>6827530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075116</v>
+        <v>120075115</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478396</v>
+        <v>478417</v>
       </c>
       <c r="R11" t="n">
-        <v>6827595</v>
+        <v>6827606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075031</v>
+        <v>120075056</v>
       </c>
       <c r="B12" t="n">
-        <v>78262</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478492</v>
+        <v>478506</v>
       </c>
       <c r="R12" t="n">
-        <v>6827538</v>
+        <v>6827552</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120074900</v>
+        <v>120075101</v>
       </c>
       <c r="B13" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
         <v>478411</v>
       </c>
       <c r="R13" t="n">
-        <v>6827584</v>
+        <v>6827532</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074902</v>
+        <v>120075109</v>
       </c>
       <c r="B14" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478397</v>
+        <v>478505</v>
       </c>
       <c r="R14" t="n">
-        <v>6827585</v>
+        <v>6827549</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074990</v>
+        <v>120075116</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,39 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478450</v>
+        <v>478396</v>
       </c>
       <c r="R15" t="n">
-        <v>6827577</v>
+        <v>6827595</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075034</v>
+        <v>120074900</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478379</v>
+        <v>478411</v>
       </c>
       <c r="R16" t="n">
-        <v>6827599</v>
+        <v>6827584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075100</v>
+        <v>120074902</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478398</v>
+        <v>478397</v>
       </c>
       <c r="R17" t="n">
-        <v>6827537</v>
+        <v>6827585</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075211</v>
+        <v>120074903</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478402</v>
+        <v>478380</v>
       </c>
       <c r="R18" t="n">
-        <v>6827537</v>
+        <v>6827599</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075209</v>
+        <v>120075031</v>
       </c>
       <c r="B19" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478401</v>
+        <v>478492</v>
       </c>
       <c r="R19" t="n">
-        <v>6827551</v>
+        <v>6827538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120074894</v>
+        <v>120075111</v>
       </c>
       <c r="B20" t="n">
-        <v>79144</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478491</v>
+        <v>478498</v>
       </c>
       <c r="R20" t="n">
-        <v>6827539</v>
+        <v>6827561</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074898</v>
+        <v>120075209</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478443</v>
+        <v>478401</v>
       </c>
       <c r="R21" t="n">
-        <v>6827578</v>
+        <v>6827551</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075109</v>
+        <v>120075033</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478505</v>
+        <v>478398</v>
       </c>
       <c r="R22" t="n">
-        <v>6827549</v>
+        <v>6827585</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075114</v>
+        <v>120075105</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478430</v>
+        <v>478466</v>
       </c>
       <c r="R23" t="n">
-        <v>6827596</v>
+        <v>6827519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075105</v>
+        <v>120075113</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478466</v>
+        <v>478441</v>
       </c>
       <c r="R24" t="n">
-        <v>6827519</v>
+        <v>6827579</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075115</v>
+        <v>120075034</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478417</v>
+        <v>478379</v>
       </c>
       <c r="R25" t="n">
-        <v>6827606</v>
+        <v>6827599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120074893</v>
+        <v>120074894</v>
       </c>
       <c r="B26" t="n">
-        <v>79144</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478394</v>
+        <v>478491</v>
       </c>
       <c r="R26" t="n">
-        <v>6827537</v>
+        <v>6827539</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075101</v>
+        <v>120074896</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478411</v>
+        <v>478480</v>
       </c>
       <c r="R27" t="n">
-        <v>6827532</v>
+        <v>6827565</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075030</v>
+        <v>120074898</v>
       </c>
       <c r="B28" t="n">
-        <v>78262</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3343,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3367,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478428</v>
+        <v>478443</v>
       </c>
       <c r="R28" t="n">
-        <v>6827530</v>
+        <v>6827578</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074896</v>
+        <v>120075210</v>
       </c>
       <c r="B29" t="n">
-        <v>79144</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478480</v>
+        <v>478399</v>
       </c>
       <c r="R29" t="n">
-        <v>6827565</v>
+        <v>6827538</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075056</v>
+        <v>120074990</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,34 +3547,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478506</v>
+        <v>478450</v>
       </c>
       <c r="R30" t="n">
-        <v>6827552</v>
+        <v>6827577</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3617,6 +3612,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074953</v>
+        <v>120075030</v>
       </c>
       <c r="B31" t="n">
-        <v>79115</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075112</v>
+        <v>120075100</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478453</v>
+        <v>478398</v>
       </c>
       <c r="R32" t="n">
-        <v>6827573</v>
+        <v>6827537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074958</v>
+        <v>120074918</v>
       </c>
       <c r="B33" t="n">
-        <v>57463</v>
+        <v>78576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478491</v>
+        <v>478466</v>
       </c>
       <c r="R33" t="n">
-        <v>6827538</v>
+        <v>6827519</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075102</v>
+        <v>120075114</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1024,7 +1024,7 @@
         <v>478430</v>
       </c>
       <c r="R5" t="n">
-        <v>6827531</v>
+        <v>6827596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075114</v>
+        <v>120075102</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1126,7 +1126,7 @@
         <v>478430</v>
       </c>
       <c r="R6" t="n">
-        <v>6827596</v>
+        <v>6827531</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075116</v>
+        <v>120074902</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478396</v>
+        <v>478397</v>
       </c>
       <c r="R15" t="n">
-        <v>6827595</v>
+        <v>6827585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120074900</v>
+        <v>120075116</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478411</v>
+        <v>478396</v>
       </c>
       <c r="R16" t="n">
-        <v>6827584</v>
+        <v>6827595</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120074902</v>
+        <v>120074900</v>
       </c>
       <c r="B17" t="n">
         <v>79160</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478397</v>
+        <v>478411</v>
       </c>
       <c r="R17" t="n">
-        <v>6827585</v>
+        <v>6827584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075211</v>
+        <v>120075030</v>
       </c>
       <c r="B2" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478402</v>
+        <v>478428</v>
       </c>
       <c r="R2" t="n">
-        <v>6827537</v>
+        <v>6827530</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075006</v>
+        <v>120075102</v>
       </c>
       <c r="B3" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478379</v>
+        <v>478430</v>
       </c>
       <c r="R3" t="n">
-        <v>6827599</v>
+        <v>6827531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075199</v>
+        <v>120074902</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478451</v>
+        <v>478397</v>
       </c>
       <c r="R4" t="n">
-        <v>6827576</v>
+        <v>6827585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075114</v>
+        <v>120074990</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478430</v>
+        <v>478450</v>
       </c>
       <c r="R5" t="n">
-        <v>6827596</v>
+        <v>6827577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075102</v>
+        <v>120075199</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478430</v>
+        <v>478451</v>
       </c>
       <c r="R6" t="n">
-        <v>6827531</v>
+        <v>6827576</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074958</v>
+        <v>120075101</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478491</v>
+        <v>478411</v>
       </c>
       <c r="R7" t="n">
-        <v>6827538</v>
+        <v>6827532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075112</v>
+        <v>120075210</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478453</v>
+        <v>478399</v>
       </c>
       <c r="R8" t="n">
-        <v>6827573</v>
+        <v>6827538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120074893</v>
+        <v>120075113</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478394</v>
+        <v>478441</v>
       </c>
       <c r="R9" t="n">
-        <v>6827537</v>
+        <v>6827579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120074953</v>
+        <v>120075114</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478428</v>
+        <v>478430</v>
       </c>
       <c r="R10" t="n">
-        <v>6827530</v>
+        <v>6827596</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075115</v>
+        <v>120075211</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478417</v>
+        <v>478402</v>
       </c>
       <c r="R11" t="n">
-        <v>6827606</v>
+        <v>6827537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075056</v>
+        <v>120074958</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478506</v>
+        <v>478491</v>
       </c>
       <c r="R12" t="n">
-        <v>6827552</v>
+        <v>6827538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075101</v>
+        <v>120075116</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478411</v>
+        <v>478396</v>
       </c>
       <c r="R13" t="n">
-        <v>6827532</v>
+        <v>6827595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075109</v>
+        <v>120075033</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478505</v>
+        <v>478398</v>
       </c>
       <c r="R14" t="n">
-        <v>6827549</v>
+        <v>6827585</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074902</v>
+        <v>120074893</v>
       </c>
       <c r="B15" t="n">
         <v>79160</v>
@@ -2041,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478397</v>
+        <v>478394</v>
       </c>
       <c r="R15" t="n">
-        <v>6827585</v>
+        <v>6827537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075116</v>
+        <v>120075109</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478396</v>
+        <v>478505</v>
       </c>
       <c r="R16" t="n">
-        <v>6827595</v>
+        <v>6827549</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120074900</v>
+        <v>120075034</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478411</v>
+        <v>478379</v>
       </c>
       <c r="R17" t="n">
-        <v>6827584</v>
+        <v>6827599</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074903</v>
+        <v>120074896</v>
       </c>
       <c r="B18" t="n">
         <v>79160</v>
@@ -2347,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478380</v>
+        <v>478480</v>
       </c>
       <c r="R18" t="n">
-        <v>6827599</v>
+        <v>6827565</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075031</v>
+        <v>120075112</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478492</v>
+        <v>478453</v>
       </c>
       <c r="R19" t="n">
-        <v>6827538</v>
+        <v>6827573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075111</v>
+        <v>120075209</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478498</v>
+        <v>478401</v>
       </c>
       <c r="R20" t="n">
-        <v>6827561</v>
+        <v>6827551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075209</v>
+        <v>120074903</v>
       </c>
       <c r="B21" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478401</v>
+        <v>478380</v>
       </c>
       <c r="R21" t="n">
-        <v>6827551</v>
+        <v>6827599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075033</v>
+        <v>120075006</v>
       </c>
       <c r="B22" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478398</v>
+        <v>478379</v>
       </c>
       <c r="R22" t="n">
-        <v>6827585</v>
+        <v>6827599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075105</v>
+        <v>120075031</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478466</v>
+        <v>478492</v>
       </c>
       <c r="R23" t="n">
-        <v>6827519</v>
+        <v>6827538</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075113</v>
+        <v>120074894</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478441</v>
+        <v>478491</v>
       </c>
       <c r="R24" t="n">
-        <v>6827579</v>
+        <v>6827539</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075034</v>
+        <v>120074898</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478379</v>
+        <v>478443</v>
       </c>
       <c r="R25" t="n">
-        <v>6827599</v>
+        <v>6827578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120074894</v>
+        <v>120075115</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478491</v>
+        <v>478417</v>
       </c>
       <c r="R26" t="n">
-        <v>6827539</v>
+        <v>6827606</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074896</v>
+        <v>120075111</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3241,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478480</v>
+        <v>478498</v>
       </c>
       <c r="R27" t="n">
-        <v>6827565</v>
+        <v>6827561</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074898</v>
+        <v>120075056</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3343,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478443</v>
+        <v>478506</v>
       </c>
       <c r="R28" t="n">
-        <v>6827578</v>
+        <v>6827552</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075210</v>
+        <v>120075105</v>
       </c>
       <c r="B29" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3445,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478399</v>
+        <v>478466</v>
       </c>
       <c r="R29" t="n">
-        <v>6827538</v>
+        <v>6827519</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074990</v>
+        <v>120074918</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>78576</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3547,39 +3557,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478450</v>
+        <v>478466</v>
       </c>
       <c r="R30" t="n">
-        <v>6827577</v>
+        <v>6827519</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3612,11 +3617,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075030</v>
+        <v>120074900</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478428</v>
+        <v>478411</v>
       </c>
       <c r="R31" t="n">
-        <v>6827530</v>
+        <v>6827584</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075100</v>
+        <v>120074953</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478398</v>
+        <v>478428</v>
       </c>
       <c r="R32" t="n">
-        <v>6827537</v>
+        <v>6827530</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074918</v>
+        <v>120075100</v>
       </c>
       <c r="B33" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478466</v>
+        <v>478398</v>
       </c>
       <c r="R33" t="n">
-        <v>6827519</v>
+        <v>6827537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075199</v>
+        <v>120075101</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478451</v>
+        <v>478411</v>
       </c>
       <c r="R6" t="n">
-        <v>6827576</v>
+        <v>6827532</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075101</v>
+        <v>120075199</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478411</v>
+        <v>478451</v>
       </c>
       <c r="R7" t="n">
-        <v>6827532</v>
+        <v>6827576</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075114</v>
+        <v>120075211</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478430</v>
+        <v>478402</v>
       </c>
       <c r="R10" t="n">
-        <v>6827596</v>
+        <v>6827537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075211</v>
+        <v>120075114</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478402</v>
+        <v>478430</v>
       </c>
       <c r="R11" t="n">
-        <v>6827537</v>
+        <v>6827596</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075105</v>
+        <v>120074918</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074918</v>
+        <v>120075105</v>
       </c>
       <c r="B30" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074953</v>
+        <v>120075100</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478428</v>
+        <v>478398</v>
       </c>
       <c r="R32" t="n">
-        <v>6827530</v>
+        <v>6827537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075100</v>
+        <v>120074953</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478398</v>
+        <v>478428</v>
       </c>
       <c r="R33" t="n">
-        <v>6827537</v>
+        <v>6827530</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075030</v>
+        <v>120075199</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478428</v>
+        <v>478451</v>
       </c>
       <c r="R2" t="n">
-        <v>6827530</v>
+        <v>6827576</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075102</v>
+        <v>120074953</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478430</v>
+        <v>478428</v>
       </c>
       <c r="R3" t="n">
-        <v>6827531</v>
+        <v>6827530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074902</v>
+        <v>120075209</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478397</v>
+        <v>478401</v>
       </c>
       <c r="R4" t="n">
-        <v>6827585</v>
+        <v>6827551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120074990</v>
+        <v>120075105</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478450</v>
+        <v>478466</v>
       </c>
       <c r="R5" t="n">
-        <v>6827577</v>
+        <v>6827519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075101</v>
+        <v>120074894</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478411</v>
+        <v>478491</v>
       </c>
       <c r="R6" t="n">
-        <v>6827532</v>
+        <v>6827539</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075199</v>
+        <v>120074990</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1197,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478451</v>
+        <v>478450</v>
       </c>
       <c r="R7" t="n">
-        <v>6827576</v>
+        <v>6827577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075210</v>
+        <v>120075115</v>
       </c>
       <c r="B8" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478399</v>
+        <v>478417</v>
       </c>
       <c r="R8" t="n">
-        <v>6827538</v>
+        <v>6827606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075113</v>
+        <v>120075034</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478441</v>
+        <v>478379</v>
       </c>
       <c r="R9" t="n">
-        <v>6827579</v>
+        <v>6827599</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075211</v>
+        <v>120075031</v>
       </c>
       <c r="B10" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478402</v>
+        <v>478492</v>
       </c>
       <c r="R10" t="n">
-        <v>6827537</v>
+        <v>6827538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075114</v>
+        <v>120075211</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478430</v>
+        <v>478402</v>
       </c>
       <c r="R11" t="n">
-        <v>6827596</v>
+        <v>6827537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120074958</v>
+        <v>120075100</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478491</v>
+        <v>478398</v>
       </c>
       <c r="R12" t="n">
-        <v>6827538</v>
+        <v>6827537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075116</v>
+        <v>120074902</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478396</v>
+        <v>478397</v>
       </c>
       <c r="R13" t="n">
-        <v>6827595</v>
+        <v>6827585</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075033</v>
+        <v>120074958</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478398</v>
+        <v>478491</v>
       </c>
       <c r="R14" t="n">
-        <v>6827585</v>
+        <v>6827538</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074893</v>
+        <v>120075056</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478394</v>
+        <v>478506</v>
       </c>
       <c r="R15" t="n">
-        <v>6827537</v>
+        <v>6827552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075109</v>
+        <v>120074896</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478505</v>
+        <v>478480</v>
       </c>
       <c r="R16" t="n">
-        <v>6827549</v>
+        <v>6827565</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075034</v>
+        <v>120075112</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478379</v>
+        <v>478453</v>
       </c>
       <c r="R17" t="n">
-        <v>6827599</v>
+        <v>6827573</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074896</v>
+        <v>120075033</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478480</v>
+        <v>478398</v>
       </c>
       <c r="R18" t="n">
-        <v>6827565</v>
+        <v>6827585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075112</v>
+        <v>120075113</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478453</v>
+        <v>478441</v>
       </c>
       <c r="R19" t="n">
-        <v>6827573</v>
+        <v>6827579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075209</v>
+        <v>120075114</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478401</v>
+        <v>478430</v>
       </c>
       <c r="R20" t="n">
-        <v>6827551</v>
+        <v>6827596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120074903</v>
+        <v>120075109</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478380</v>
+        <v>478505</v>
       </c>
       <c r="R21" t="n">
-        <v>6827599</v>
+        <v>6827549</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075006</v>
+        <v>120074918</v>
       </c>
       <c r="B22" t="n">
-        <v>78279</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478379</v>
+        <v>478466</v>
       </c>
       <c r="R22" t="n">
-        <v>6827599</v>
+        <v>6827519</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075031</v>
+        <v>120074898</v>
       </c>
       <c r="B23" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478492</v>
+        <v>478443</v>
       </c>
       <c r="R23" t="n">
-        <v>6827538</v>
+        <v>6827578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074894</v>
+        <v>120074903</v>
       </c>
       <c r="B24" t="n">
         <v>79160</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478491</v>
+        <v>478380</v>
       </c>
       <c r="R24" t="n">
-        <v>6827539</v>
+        <v>6827599</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120074898</v>
+        <v>120074900</v>
       </c>
       <c r="B25" t="n">
         <v>79160</v>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478443</v>
+        <v>478411</v>
       </c>
       <c r="R25" t="n">
-        <v>6827578</v>
+        <v>6827584</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075115</v>
+        <v>120075210</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478417</v>
+        <v>478399</v>
       </c>
       <c r="R26" t="n">
-        <v>6827606</v>
+        <v>6827538</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075111</v>
+        <v>120074893</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478498</v>
+        <v>478394</v>
       </c>
       <c r="R27" t="n">
-        <v>6827561</v>
+        <v>6827537</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075056</v>
+        <v>120075111</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478506</v>
+        <v>478498</v>
       </c>
       <c r="R28" t="n">
-        <v>6827552</v>
+        <v>6827561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074918</v>
+        <v>120075101</v>
       </c>
       <c r="B29" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478466</v>
+        <v>478411</v>
       </c>
       <c r="R29" t="n">
-        <v>6827519</v>
+        <v>6827532</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075105</v>
+        <v>120075116</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478466</v>
+        <v>478396</v>
       </c>
       <c r="R30" t="n">
-        <v>6827519</v>
+        <v>6827595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074900</v>
+        <v>120075030</v>
       </c>
       <c r="B31" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478411</v>
+        <v>478428</v>
       </c>
       <c r="R31" t="n">
-        <v>6827584</v>
+        <v>6827530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075100</v>
+        <v>120075102</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478398</v>
+        <v>478430</v>
       </c>
       <c r="R32" t="n">
-        <v>6827537</v>
+        <v>6827531</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074953</v>
+        <v>120075006</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>78279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478428</v>
+        <v>478379</v>
       </c>
       <c r="R33" t="n">
-        <v>6827530</v>
+        <v>6827599</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075199</v>
+        <v>120075210</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478451</v>
+        <v>478399</v>
       </c>
       <c r="R2" t="n">
-        <v>6827576</v>
+        <v>6827538</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074953</v>
+        <v>120074918</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478428</v>
+        <v>478466</v>
       </c>
       <c r="R3" t="n">
-        <v>6827530</v>
+        <v>6827519</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075209</v>
+        <v>120074894</v>
       </c>
       <c r="B4" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478401</v>
+        <v>478491</v>
       </c>
       <c r="R4" t="n">
-        <v>6827551</v>
+        <v>6827539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075105</v>
+        <v>120075101</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478466</v>
+        <v>478411</v>
       </c>
       <c r="R5" t="n">
-        <v>6827519</v>
+        <v>6827532</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120074894</v>
+        <v>120075100</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478491</v>
+        <v>478398</v>
       </c>
       <c r="R6" t="n">
-        <v>6827539</v>
+        <v>6827537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074990</v>
+        <v>120075109</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478450</v>
+        <v>478505</v>
       </c>
       <c r="R7" t="n">
-        <v>6827577</v>
+        <v>6827549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075115</v>
+        <v>120074958</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478417</v>
+        <v>478491</v>
       </c>
       <c r="R8" t="n">
-        <v>6827606</v>
+        <v>6827538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075034</v>
+        <v>120075211</v>
       </c>
       <c r="B9" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478379</v>
+        <v>478402</v>
       </c>
       <c r="R9" t="n">
-        <v>6827599</v>
+        <v>6827537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075031</v>
+        <v>120075102</v>
       </c>
       <c r="B10" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478492</v>
+        <v>478430</v>
       </c>
       <c r="R10" t="n">
-        <v>6827538</v>
+        <v>6827531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075211</v>
+        <v>120075112</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478402</v>
+        <v>478453</v>
       </c>
       <c r="R11" t="n">
-        <v>6827537</v>
+        <v>6827573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075100</v>
+        <v>120075113</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478398</v>
+        <v>478441</v>
       </c>
       <c r="R12" t="n">
-        <v>6827537</v>
+        <v>6827579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120074902</v>
+        <v>120075116</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478397</v>
+        <v>478396</v>
       </c>
       <c r="R13" t="n">
-        <v>6827585</v>
+        <v>6827595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120074958</v>
+        <v>120075199</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>91858</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478491</v>
+        <v>478451</v>
       </c>
       <c r="R14" t="n">
-        <v>6827538</v>
+        <v>6827576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075056</v>
+        <v>120074990</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,34 +2017,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478506</v>
+        <v>478450</v>
       </c>
       <c r="R15" t="n">
-        <v>6827552</v>
+        <v>6827577</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120074896</v>
+        <v>120075115</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478480</v>
+        <v>478417</v>
       </c>
       <c r="R16" t="n">
-        <v>6827565</v>
+        <v>6827606</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075112</v>
+        <v>120074893</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478453</v>
+        <v>478394</v>
       </c>
       <c r="R17" t="n">
-        <v>6827573</v>
+        <v>6827537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120075033</v>
+        <v>120074902</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478398</v>
+        <v>478397</v>
       </c>
       <c r="R18" t="n">
         <v>6827585</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075113</v>
+        <v>120075031</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478441</v>
+        <v>478492</v>
       </c>
       <c r="R19" t="n">
-        <v>6827579</v>
+        <v>6827538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075114</v>
+        <v>120075030</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478430</v>
+        <v>478428</v>
       </c>
       <c r="R20" t="n">
-        <v>6827596</v>
+        <v>6827530</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075109</v>
+        <v>120075033</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478505</v>
+        <v>478398</v>
       </c>
       <c r="R21" t="n">
-        <v>6827549</v>
+        <v>6827585</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120074918</v>
+        <v>120075111</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478466</v>
+        <v>478498</v>
       </c>
       <c r="R22" t="n">
-        <v>6827519</v>
+        <v>6827561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074898</v>
+        <v>120075105</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478443</v>
+        <v>478466</v>
       </c>
       <c r="R23" t="n">
-        <v>6827578</v>
+        <v>6827519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074903</v>
+        <v>120074900</v>
       </c>
       <c r="B24" t="n">
         <v>79160</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478380</v>
+        <v>478411</v>
       </c>
       <c r="R24" t="n">
-        <v>6827599</v>
+        <v>6827584</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120074900</v>
+        <v>120074903</v>
       </c>
       <c r="B25" t="n">
         <v>79160</v>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478411</v>
+        <v>478380</v>
       </c>
       <c r="R25" t="n">
-        <v>6827584</v>
+        <v>6827599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075210</v>
+        <v>120075034</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478399</v>
+        <v>478379</v>
       </c>
       <c r="R26" t="n">
-        <v>6827538</v>
+        <v>6827599</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120074893</v>
+        <v>120075209</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478394</v>
+        <v>478401</v>
       </c>
       <c r="R27" t="n">
-        <v>6827537</v>
+        <v>6827551</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075111</v>
+        <v>120075006</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478498</v>
+        <v>478379</v>
       </c>
       <c r="R28" t="n">
-        <v>6827561</v>
+        <v>6827599</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075101</v>
+        <v>120074896</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478411</v>
+        <v>478480</v>
       </c>
       <c r="R29" t="n">
-        <v>6827532</v>
+        <v>6827565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075116</v>
+        <v>120075114</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478396</v>
+        <v>478430</v>
       </c>
       <c r="R30" t="n">
-        <v>6827595</v>
+        <v>6827596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075030</v>
+        <v>120075056</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478428</v>
+        <v>478506</v>
       </c>
       <c r="R31" t="n">
-        <v>6827530</v>
+        <v>6827552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075102</v>
+        <v>120074898</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478430</v>
+        <v>478443</v>
       </c>
       <c r="R32" t="n">
-        <v>6827531</v>
+        <v>6827578</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075006</v>
+        <v>120074953</v>
       </c>
       <c r="B33" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478379</v>
+        <v>478428</v>
       </c>
       <c r="R33" t="n">
-        <v>6827599</v>
+        <v>6827530</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075210</v>
+        <v>120075101</v>
       </c>
       <c r="B2" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478399</v>
+        <v>478411</v>
       </c>
       <c r="R2" t="n">
-        <v>6827538</v>
+        <v>6827532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074918</v>
+        <v>120075211</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478466</v>
+        <v>478402</v>
       </c>
       <c r="R3" t="n">
-        <v>6827519</v>
+        <v>6827537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120074894</v>
+        <v>120075030</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478491</v>
+        <v>478428</v>
       </c>
       <c r="R4" t="n">
-        <v>6827539</v>
+        <v>6827530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075101</v>
+        <v>120075111</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478411</v>
+        <v>478498</v>
       </c>
       <c r="R5" t="n">
-        <v>6827532</v>
+        <v>6827561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075100</v>
+        <v>120075115</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478398</v>
+        <v>478417</v>
       </c>
       <c r="R6" t="n">
-        <v>6827537</v>
+        <v>6827606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075109</v>
+        <v>120074896</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478505</v>
+        <v>478480</v>
       </c>
       <c r="R7" t="n">
-        <v>6827549</v>
+        <v>6827565</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120074958</v>
+        <v>120075109</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478491</v>
+        <v>478505</v>
       </c>
       <c r="R8" t="n">
-        <v>6827538</v>
+        <v>6827549</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120075211</v>
+        <v>120074958</v>
       </c>
       <c r="B9" t="n">
-        <v>78187</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478402</v>
+        <v>478491</v>
       </c>
       <c r="R9" t="n">
-        <v>6827537</v>
+        <v>6827538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075102</v>
+        <v>120075100</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478430</v>
+        <v>478398</v>
       </c>
       <c r="R10" t="n">
-        <v>6827531</v>
+        <v>6827537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075112</v>
+        <v>120075209</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478453</v>
+        <v>478401</v>
       </c>
       <c r="R11" t="n">
-        <v>6827573</v>
+        <v>6827551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075113</v>
+        <v>120075033</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478441</v>
+        <v>478398</v>
       </c>
       <c r="R12" t="n">
-        <v>6827579</v>
+        <v>6827585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075116</v>
+        <v>120074990</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1813,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478396</v>
+        <v>478450</v>
       </c>
       <c r="R13" t="n">
-        <v>6827595</v>
+        <v>6827577</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075199</v>
+        <v>120075113</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478451</v>
+        <v>478441</v>
       </c>
       <c r="R14" t="n">
-        <v>6827576</v>
+        <v>6827579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074990</v>
+        <v>120074900</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,39 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478450</v>
+        <v>478411</v>
       </c>
       <c r="R15" t="n">
-        <v>6827577</v>
+        <v>6827584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075115</v>
+        <v>120075034</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478417</v>
+        <v>478379</v>
       </c>
       <c r="R16" t="n">
-        <v>6827606</v>
+        <v>6827599</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120074893</v>
+        <v>120075114</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478394</v>
+        <v>478430</v>
       </c>
       <c r="R17" t="n">
-        <v>6827537</v>
+        <v>6827596</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074902</v>
+        <v>120074893</v>
       </c>
       <c r="B18" t="n">
         <v>79160</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478397</v>
+        <v>478394</v>
       </c>
       <c r="R18" t="n">
-        <v>6827585</v>
+        <v>6827537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075031</v>
+        <v>120074902</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478492</v>
+        <v>478397</v>
       </c>
       <c r="R19" t="n">
-        <v>6827538</v>
+        <v>6827585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075030</v>
+        <v>120075102</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478428</v>
+        <v>478430</v>
       </c>
       <c r="R20" t="n">
-        <v>6827530</v>
+        <v>6827531</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075033</v>
+        <v>120075056</v>
       </c>
       <c r="B21" t="n">
-        <v>78278</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478398</v>
+        <v>478506</v>
       </c>
       <c r="R21" t="n">
-        <v>6827585</v>
+        <v>6827552</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075111</v>
+        <v>120074903</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478498</v>
+        <v>478380</v>
       </c>
       <c r="R22" t="n">
-        <v>6827561</v>
+        <v>6827599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075105</v>
+        <v>120075112</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478466</v>
+        <v>478453</v>
       </c>
       <c r="R23" t="n">
-        <v>6827519</v>
+        <v>6827573</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120074900</v>
+        <v>120075105</v>
       </c>
       <c r="B24" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478411</v>
+        <v>478466</v>
       </c>
       <c r="R24" t="n">
-        <v>6827584</v>
+        <v>6827519</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120074903</v>
+        <v>120075116</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478380</v>
+        <v>478396</v>
       </c>
       <c r="R25" t="n">
-        <v>6827599</v>
+        <v>6827595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075034</v>
+        <v>120075210</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478379</v>
+        <v>478399</v>
       </c>
       <c r="R26" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075209</v>
+        <v>120075031</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478401</v>
+        <v>478492</v>
       </c>
       <c r="R27" t="n">
-        <v>6827551</v>
+        <v>6827538</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075006</v>
+        <v>120075199</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478379</v>
+        <v>478451</v>
       </c>
       <c r="R28" t="n">
-        <v>6827599</v>
+        <v>6827576</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074896</v>
+        <v>120074894</v>
       </c>
       <c r="B29" t="n">
         <v>79160</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478480</v>
+        <v>478491</v>
       </c>
       <c r="R29" t="n">
-        <v>6827565</v>
+        <v>6827539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075114</v>
+        <v>120074898</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478430</v>
+        <v>478443</v>
       </c>
       <c r="R30" t="n">
-        <v>6827596</v>
+        <v>6827578</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120075056</v>
+        <v>120074953</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478506</v>
+        <v>478428</v>
       </c>
       <c r="R31" t="n">
-        <v>6827552</v>
+        <v>6827530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074898</v>
+        <v>120075006</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>78279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478443</v>
+        <v>478379</v>
       </c>
       <c r="R32" t="n">
-        <v>6827578</v>
+        <v>6827599</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074953</v>
+        <v>120074918</v>
       </c>
       <c r="B33" t="n">
-        <v>79131</v>
+        <v>78576</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478428</v>
+        <v>478466</v>
       </c>
       <c r="R33" t="n">
-        <v>6827530</v>
+        <v>6827519</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075101</v>
+        <v>120075056</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478411</v>
+        <v>478506</v>
       </c>
       <c r="R2" t="n">
-        <v>6827532</v>
+        <v>6827552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120075211</v>
+        <v>120074903</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478402</v>
+        <v>478380</v>
       </c>
       <c r="R3" t="n">
-        <v>6827537</v>
+        <v>6827599</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075030</v>
+        <v>120075109</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478428</v>
+        <v>478505</v>
       </c>
       <c r="R4" t="n">
-        <v>6827530</v>
+        <v>6827549</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120075111</v>
+        <v>120074893</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478498</v>
+        <v>478394</v>
       </c>
       <c r="R5" t="n">
-        <v>6827561</v>
+        <v>6827537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075115</v>
+        <v>120075030</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478417</v>
+        <v>478428</v>
       </c>
       <c r="R6" t="n">
-        <v>6827606</v>
+        <v>6827530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120074896</v>
+        <v>120075102</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478480</v>
+        <v>478430</v>
       </c>
       <c r="R7" t="n">
-        <v>6827565</v>
+        <v>6827531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075109</v>
+        <v>120075116</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478505</v>
+        <v>478396</v>
       </c>
       <c r="R8" t="n">
-        <v>6827549</v>
+        <v>6827595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075100</v>
+        <v>120075111</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478398</v>
+        <v>478498</v>
       </c>
       <c r="R10" t="n">
-        <v>6827537</v>
+        <v>6827561</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075209</v>
+        <v>120075031</v>
       </c>
       <c r="B11" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478401</v>
+        <v>478492</v>
       </c>
       <c r="R11" t="n">
-        <v>6827551</v>
+        <v>6827538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075033</v>
+        <v>120075112</v>
       </c>
       <c r="B12" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478398</v>
+        <v>478453</v>
       </c>
       <c r="R12" t="n">
-        <v>6827585</v>
+        <v>6827573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120074990</v>
+        <v>120075105</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478450</v>
+        <v>478466</v>
       </c>
       <c r="R13" t="n">
-        <v>6827577</v>
+        <v>6827519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075113</v>
+        <v>120075100</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478441</v>
+        <v>478398</v>
       </c>
       <c r="R14" t="n">
-        <v>6827579</v>
+        <v>6827537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120074900</v>
+        <v>120075211</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478411</v>
+        <v>478402</v>
       </c>
       <c r="R15" t="n">
-        <v>6827584</v>
+        <v>6827537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075034</v>
+        <v>120075210</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478379</v>
+        <v>478399</v>
       </c>
       <c r="R16" t="n">
-        <v>6827599</v>
+        <v>6827538</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120075114</v>
+        <v>120074894</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478430</v>
+        <v>478491</v>
       </c>
       <c r="R17" t="n">
-        <v>6827596</v>
+        <v>6827539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074893</v>
+        <v>120074900</v>
       </c>
       <c r="B18" t="n">
         <v>79160</v>
@@ -2357,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478394</v>
+        <v>478411</v>
       </c>
       <c r="R18" t="n">
-        <v>6827537</v>
+        <v>6827584</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120074902</v>
+        <v>120075115</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478397</v>
+        <v>478417</v>
       </c>
       <c r="R19" t="n">
-        <v>6827585</v>
+        <v>6827606</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075102</v>
+        <v>120075199</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478430</v>
+        <v>478451</v>
       </c>
       <c r="R20" t="n">
-        <v>6827531</v>
+        <v>6827576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075056</v>
+        <v>120075006</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478506</v>
+        <v>478379</v>
       </c>
       <c r="R21" t="n">
-        <v>6827552</v>
+        <v>6827599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120074903</v>
+        <v>120075209</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478380</v>
+        <v>478401</v>
       </c>
       <c r="R22" t="n">
-        <v>6827599</v>
+        <v>6827551</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075112</v>
+        <v>120074896</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478453</v>
+        <v>478480</v>
       </c>
       <c r="R23" t="n">
-        <v>6827573</v>
+        <v>6827565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2929,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075105</v>
+        <v>120075101</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2969,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478466</v>
+        <v>478411</v>
       </c>
       <c r="R24" t="n">
-        <v>6827519</v>
+        <v>6827532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120075116</v>
+        <v>120074990</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,34 +3037,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478396</v>
+        <v>478450</v>
       </c>
       <c r="R25" t="n">
-        <v>6827595</v>
+        <v>6827577</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,6 +3102,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120075210</v>
+        <v>120074953</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>79131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478399</v>
+        <v>478428</v>
       </c>
       <c r="R26" t="n">
-        <v>6827538</v>
+        <v>6827530</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075031</v>
+        <v>120075113</v>
       </c>
       <c r="B27" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478492</v>
+        <v>478441</v>
       </c>
       <c r="R27" t="n">
-        <v>6827538</v>
+        <v>6827579</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120075199</v>
+        <v>120074898</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478451</v>
+        <v>478443</v>
       </c>
       <c r="R28" t="n">
-        <v>6827576</v>
+        <v>6827578</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120074894</v>
+        <v>120075034</v>
       </c>
       <c r="B29" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478491</v>
+        <v>478379</v>
       </c>
       <c r="R29" t="n">
-        <v>6827539</v>
+        <v>6827599</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120074898</v>
+        <v>120075114</v>
       </c>
       <c r="B30" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478443</v>
+        <v>478430</v>
       </c>
       <c r="R30" t="n">
-        <v>6827578</v>
+        <v>6827596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074953</v>
+        <v>120074918</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>78576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478428</v>
+        <v>478466</v>
       </c>
       <c r="R31" t="n">
-        <v>6827530</v>
+        <v>6827519</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120075006</v>
+        <v>120074902</v>
       </c>
       <c r="B32" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478379</v>
+        <v>478397</v>
       </c>
       <c r="R32" t="n">
-        <v>6827599</v>
+        <v>6827585</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120074918</v>
+        <v>120075033</v>
       </c>
       <c r="B33" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478466</v>
+        <v>478398</v>
       </c>
       <c r="R33" t="n">
-        <v>6827519</v>
+        <v>6827585</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120075056</v>
+        <v>120075109</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478506</v>
+        <v>478505</v>
       </c>
       <c r="R2" t="n">
-        <v>6827552</v>
+        <v>6827549</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120074903</v>
+        <v>120075211</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478380</v>
+        <v>478402</v>
       </c>
       <c r="R3" t="n">
-        <v>6827599</v>
+        <v>6827537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120075109</v>
+        <v>120075209</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478505</v>
+        <v>478401</v>
       </c>
       <c r="R4" t="n">
-        <v>6827549</v>
+        <v>6827551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120074893</v>
+        <v>120074900</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478394</v>
+        <v>478411</v>
       </c>
       <c r="R5" t="n">
-        <v>6827537</v>
+        <v>6827584</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120075030</v>
+        <v>120074953</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120075102</v>
+        <v>120075006</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478430</v>
+        <v>478379</v>
       </c>
       <c r="R7" t="n">
-        <v>6827531</v>
+        <v>6827599</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120075116</v>
+        <v>120075114</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478396</v>
+        <v>478430</v>
       </c>
       <c r="R8" t="n">
-        <v>6827595</v>
+        <v>6827596</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120074958</v>
+        <v>120075056</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478491</v>
+        <v>478506</v>
       </c>
       <c r="R9" t="n">
-        <v>6827538</v>
+        <v>6827552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120075111</v>
+        <v>120075100</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478498</v>
+        <v>478398</v>
       </c>
       <c r="R10" t="n">
-        <v>6827561</v>
+        <v>6827537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120075031</v>
+        <v>120074918</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478492</v>
+        <v>478466</v>
       </c>
       <c r="R11" t="n">
-        <v>6827538</v>
+        <v>6827519</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120075112</v>
+        <v>120074898</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478453</v>
+        <v>478443</v>
       </c>
       <c r="R12" t="n">
-        <v>6827573</v>
+        <v>6827578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120075105</v>
+        <v>120075112</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478466</v>
+        <v>478453</v>
       </c>
       <c r="R13" t="n">
-        <v>6827519</v>
+        <v>6827573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120075100</v>
+        <v>120075115</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478398</v>
+        <v>478417</v>
       </c>
       <c r="R14" t="n">
-        <v>6827537</v>
+        <v>6827606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120075211</v>
+        <v>120075111</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478402</v>
+        <v>478498</v>
       </c>
       <c r="R15" t="n">
-        <v>6827537</v>
+        <v>6827561</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120075210</v>
+        <v>120075116</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478399</v>
+        <v>478396</v>
       </c>
       <c r="R16" t="n">
-        <v>6827538</v>
+        <v>6827595</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120074894</v>
+        <v>120075105</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478491</v>
+        <v>478466</v>
       </c>
       <c r="R17" t="n">
-        <v>6827539</v>
+        <v>6827519</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120074900</v>
+        <v>120075030</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478411</v>
+        <v>478428</v>
       </c>
       <c r="R18" t="n">
-        <v>6827584</v>
+        <v>6827530</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120075115</v>
+        <v>120075210</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478417</v>
+        <v>478399</v>
       </c>
       <c r="R19" t="n">
-        <v>6827606</v>
+        <v>6827538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120075199</v>
+        <v>120075031</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478451</v>
+        <v>478492</v>
       </c>
       <c r="R20" t="n">
-        <v>6827576</v>
+        <v>6827538</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120075006</v>
+        <v>120075199</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478379</v>
+        <v>478451</v>
       </c>
       <c r="R21" t="n">
-        <v>6827599</v>
+        <v>6827576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075209</v>
+        <v>120075113</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478401</v>
+        <v>478441</v>
       </c>
       <c r="R22" t="n">
-        <v>6827551</v>
+        <v>6827579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120074896</v>
+        <v>120075102</v>
       </c>
       <c r="B23" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478480</v>
+        <v>478430</v>
       </c>
       <c r="R23" t="n">
-        <v>6827565</v>
+        <v>6827531</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075101</v>
+        <v>120075034</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478411</v>
+        <v>478379</v>
       </c>
       <c r="R24" t="n">
-        <v>6827532</v>
+        <v>6827599</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120074990</v>
+        <v>120075101</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,39 +3037,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478450</v>
+        <v>478411</v>
       </c>
       <c r="R25" t="n">
-        <v>6827577</v>
+        <v>6827532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,11 +3097,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120074953</v>
+        <v>120074902</v>
       </c>
       <c r="B26" t="n">
-        <v>79131</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478428</v>
+        <v>478397</v>
       </c>
       <c r="R26" t="n">
-        <v>6827530</v>
+        <v>6827585</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3235,10 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120075113</v>
+        <v>120074990</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,34 +3241,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hevoslamm, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478441</v>
+        <v>478450</v>
       </c>
       <c r="R27" t="n">
-        <v>6827579</v>
+        <v>6827577</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3306,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,7 +3337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120074898</v>
+        <v>120074894</v>
       </c>
       <c r="B28" t="n">
         <v>79160</v>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478443</v>
+        <v>478491</v>
       </c>
       <c r="R28" t="n">
-        <v>6827578</v>
+        <v>6827539</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120075034</v>
+        <v>120074893</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478379</v>
+        <v>478394</v>
       </c>
       <c r="R29" t="n">
-        <v>6827599</v>
+        <v>6827537</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120075114</v>
+        <v>120075033</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478430</v>
+        <v>478398</v>
       </c>
       <c r="R30" t="n">
-        <v>6827596</v>
+        <v>6827585</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120074918</v>
+        <v>120074958</v>
       </c>
       <c r="B31" t="n">
-        <v>78576</v>
+        <v>57473</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478466</v>
+        <v>478491</v>
       </c>
       <c r="R31" t="n">
-        <v>6827519</v>
+        <v>6827538</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120074902</v>
+        <v>120074903</v>
       </c>
       <c r="B32" t="n">
         <v>79160</v>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478397</v>
+        <v>478380</v>
       </c>
       <c r="R32" t="n">
-        <v>6827585</v>
+        <v>6827599</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120075033</v>
+        <v>120074896</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478398</v>
+        <v>478480</v>
       </c>
       <c r="R33" t="n">
-        <v>6827585</v>
+        <v>6827565</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -2715,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120075113</v>
+        <v>120075034</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478441</v>
+        <v>478379</v>
       </c>
       <c r="R22" t="n">
-        <v>6827579</v>
+        <v>6827599</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120075102</v>
+        <v>120075113</v>
       </c>
       <c r="B23" t="n">
         <v>78542</v>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478430</v>
+        <v>478441</v>
       </c>
       <c r="R23" t="n">
-        <v>6827531</v>
+        <v>6827579</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120075034</v>
+        <v>120075102</v>
       </c>
       <c r="B24" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478379</v>
+        <v>478430</v>
       </c>
       <c r="R24" t="n">
-        <v>6827599</v>
+        <v>6827531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>120074990</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 32988-2023 artfynd.xlsx
+++ b/artfynd/A 32988-2023 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>120074990</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
